--- a/data/trans_orig/IP31KM15_2023-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/IP31KM15_2023-Provincia-trans_orig.xlsx
@@ -541,7 +541,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -552,7 +552,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -720,72 +720,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>29342</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>23766</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>35510</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>48,69%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>39,44%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>58,93%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>56</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>39490</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>28814</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>47525</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>55,31%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>40,36%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>66,56%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>46</t>
-        </is>
-      </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>34557</t>
+          <t>33075</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>27088</t>
+          <t>27416</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>42602</t>
+          <t>38217</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>46,32%</t>
+          <t>60,22%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>36,31%</t>
+          <t>49,92%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>57,1%</t>
+          <t>69,58%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>74048</t>
+          <t>62418</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>60152</t>
+          <t>53718</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>85357</t>
+          <t>70900</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>50,72%</t>
+          <t>54,19%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>41,2%</t>
+          <t>46,64%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>58,46%</t>
+          <t>61,55%</t>
         </is>
       </c>
     </row>
@@ -833,72 +833,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>30921</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>24753</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>36497</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>51,31%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>41,07%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>60,56%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>36</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>31910</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>23875</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>42586</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>44,69%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>33,44%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>59,64%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>47</t>
-        </is>
-      </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>40050</t>
+          <t>21847</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>32005</t>
+          <t>16705</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>47519</t>
+          <t>27506</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>53,68%</t>
+          <t>39,78%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>42,9%</t>
+          <t>30,42%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>63,69%</t>
+          <t>50,08%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>71959</t>
+          <t>52768</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>60650</t>
+          <t>44286</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>85855</t>
+          <t>61468</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>49,28%</t>
+          <t>45,81%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>41,54%</t>
+          <t>38,45%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>58,8%</t>
+          <t>53,36%</t>
         </is>
       </c>
     </row>
@@ -946,57 +946,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>93</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>60263</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>60263</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>60263</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>92</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>71400</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>71400</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>71400</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>93</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>74607</t>
+          <t>54922</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>74607</t>
+          <t>54922</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>74607</t>
+          <t>54922</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>146007</t>
+          <t>115186</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>146007</t>
+          <t>115186</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>146007</t>
+          <t>115186</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1063,72 +1063,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>38606</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>27911</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>50038</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>33,58%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>24,28%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>43,53%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>53</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>37058</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>14822</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>50949</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>29,49%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>11,8%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>40,55%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>42533</t>
+          <t>37264</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>31203</t>
+          <t>28863</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>55084</t>
+          <t>45999</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>33,64%</t>
+          <t>37,51%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>24,68%</t>
+          <t>29,06%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>43,57%</t>
+          <t>46,31%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1138,32 +1138,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>79591</t>
+          <t>75869</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>52476</t>
+          <t>63371</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>97677</t>
+          <t>88489</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>31,57%</t>
+          <t>35,41%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>20,82%</t>
+          <t>29,57%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>38,75%</t>
+          <t>41,3%</t>
         </is>
       </c>
     </row>
@@ -1176,72 +1176,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>103</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>76345</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>64913</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>87040</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>66,42%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>56,47%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>75,72%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>87</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>88591</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>74700</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>110827</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>70,51%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>59,45%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>88,2%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>103</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>83890</t>
+          <t>62069</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>71339</t>
+          <t>53334</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>95220</t>
+          <t>70470</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>66,36%</t>
+          <t>62,49%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>56,43%</t>
+          <t>53,69%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>75,32%</t>
+          <t>70,94%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1251,32 +1251,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>172480</t>
+          <t>138415</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>154394</t>
+          <t>125795</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>199595</t>
+          <t>150913</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>68,43%</t>
+          <t>64,59%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>61,25%</t>
+          <t>58,7%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>79,18%</t>
+          <t>70,43%</t>
         </is>
       </c>
     </row>
@@ -1289,57 +1289,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>153</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>114951</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>114951</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>114951</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>140</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>125649</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>125649</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>125649</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>153</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>126423</t>
+          <t>99333</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>126423</t>
+          <t>99333</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>126423</t>
+          <t>99333</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1364,17 +1364,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>252071</t>
+          <t>214284</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>252071</t>
+          <t>214284</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>252071</t>
+          <t>214284</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1406,72 +1406,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>22173</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>16719</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>28393</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>38,7%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>29,18%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>49,55%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>45</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>27234</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>21917</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>32918</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>49,02%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>39,45%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>59,26%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>38</t>
-        </is>
-      </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>24767</t>
+          <t>26121</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>18558</t>
+          <t>20503</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>32206</t>
+          <t>32121</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>38,32%</t>
+          <t>48,27%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>28,71%</t>
+          <t>37,89%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>49,83%</t>
+          <t>59,36%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1481,32 +1481,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>52001</t>
+          <t>48294</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>44084</t>
+          <t>40894</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>60510</t>
+          <t>56821</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>43,27%</t>
+          <t>43,35%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>36,68%</t>
+          <t>36,71%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>50,35%</t>
+          <t>51,0%</t>
         </is>
       </c>
     </row>
@@ -1519,72 +1519,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>35126</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>28906</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>40580</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>61,3%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>50,45%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>70,82%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>46</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>28318</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>22634</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>33635</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>50,98%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>40,74%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>60,55%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>57</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>39866</t>
+          <t>27991</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>32427</t>
+          <t>21991</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>46075</t>
+          <t>33609</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>61,68%</t>
+          <t>51,73%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>50,17%</t>
+          <t>40,64%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>71,29%</t>
+          <t>62,11%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1594,32 +1594,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>68184</t>
+          <t>63117</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>59675</t>
+          <t>54590</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>76101</t>
+          <t>70517</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>56,73%</t>
+          <t>56,65%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>49,65%</t>
+          <t>49,0%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>63,32%</t>
+          <t>63,29%</t>
         </is>
       </c>
     </row>
@@ -1632,57 +1632,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>95</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>57299</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>57299</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>57299</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>91</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>55552</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>55552</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>55552</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>95</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>64633</t>
+          <t>54112</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>64633</t>
+          <t>54112</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>64633</t>
+          <t>54112</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>120185</t>
+          <t>111411</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>120185</t>
+          <t>111411</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>120185</t>
+          <t>111411</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1749,72 +1749,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>46351</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>36553</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>56146</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>66,39%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>52,36%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>80,42%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>65</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>49572</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>41641</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>55117</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>71,14%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>59,76%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>79,1%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>50092</t>
+          <t>50429</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>40209</t>
+          <t>43201</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>61455</t>
+          <t>56701</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>66,46%</t>
+          <t>71,57%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>53,35%</t>
+          <t>61,31%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>81,54%</t>
+          <t>80,47%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,32 +1824,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>99665</t>
+          <t>96780</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>86400</t>
+          <t>85165</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>111995</t>
+          <t>108823</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>68,71%</t>
+          <t>68,99%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>59,57%</t>
+          <t>60,71%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>77,21%</t>
+          <t>77,58%</t>
         </is>
       </c>
     </row>
@@ -1862,72 +1862,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>23465</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>13670</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>33263</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>33,61%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>19,58%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>47,64%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>28</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>20110</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>14565</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>28041</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>28,86%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>20,9%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>40,24%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>25275</t>
+          <t>20033</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>13912</t>
+          <t>13761</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>35158</t>
+          <t>27261</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>33,54%</t>
+          <t>28,43%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>18,46%</t>
+          <t>19,53%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>46,65%</t>
+          <t>38,69%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,32 +1937,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>45384</t>
+          <t>43498</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>33054</t>
+          <t>31455</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>58649</t>
+          <t>55113</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>31,29%</t>
+          <t>31,01%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>22,79%</t>
+          <t>22,42%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>40,43%</t>
+          <t>39,29%</t>
         </is>
       </c>
     </row>
@@ -1975,57 +1975,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>69816</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>69816</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>69816</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>93</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>69682</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>69682</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>69682</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>63</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>75367</t>
+          <t>70462</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>75367</t>
+          <t>70462</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>75367</t>
+          <t>70462</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2050,17 +2050,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>145049</t>
+          <t>140278</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>145049</t>
+          <t>140278</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>145049</t>
+          <t>140278</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2097,34 +2097,34 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>32544</t>
+          <t>35336</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>29644</t>
+          <t>30893</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>33670</t>
+          <t>37664</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
+          <t>89,28%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>78,05%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
           <t>95,16%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>86,68%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>98,45%</t>
-        </is>
-      </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
           <t>64</t>
@@ -2132,32 +2132,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>36487</t>
+          <t>33703</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>32528</t>
+          <t>30950</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>38972</t>
+          <t>34832</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>89,61%</t>
+          <t>95,29%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>79,88%</t>
+          <t>87,5%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>95,71%</t>
+          <t>98,48%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,32 +2167,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>69030</t>
+          <t>69040</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>64504</t>
+          <t>64371</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>71822</t>
+          <t>71721</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>92,14%</t>
+          <t>92,12%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>86,1%</t>
+          <t>85,89%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>95,87%</t>
+          <t>95,69%</t>
         </is>
       </c>
     </row>
@@ -2205,72 +2205,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>4243</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>1915</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>8686</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>10,72%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>4,84%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>21,95%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>1656</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>530</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>4556</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>4,84%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>1,55%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>13,32%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>4232</t>
+          <t>1667</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1747</t>
+          <t>538</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>8191</t>
+          <t>4420</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>10,39%</t>
+          <t>4,71%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>4,29%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>20,12%</t>
+          <t>12,5%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,32 +2280,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>5889</t>
+          <t>5909</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>3097</t>
+          <t>3228</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>10415</t>
+          <t>10578</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>7,86%</t>
+          <t>7,88%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>4,13%</t>
+          <t>4,31%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>13,9%</t>
+          <t>14,11%</t>
         </is>
       </c>
     </row>
@@ -2318,57 +2318,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>71</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>39579</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>39579</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>39579</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>67</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>34200</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>34200</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>34200</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>71</t>
-        </is>
-      </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>40719</t>
+          <t>35370</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>40719</t>
+          <t>35370</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>40719</t>
+          <t>35370</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2393,17 +2393,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>74919</t>
+          <t>74949</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>74919</t>
+          <t>74949</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>74919</t>
+          <t>74949</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2435,72 +2435,72 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>14229</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>9813</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>18957</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>30,14%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>20,79%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>40,16%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>20</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>12399</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>8254</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>17824</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>27,99%</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>18,64%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>40,24%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>16446</t>
+          <t>12364</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>11369</t>
+          <t>7616</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>22022</t>
+          <t>16788</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>30,58%</t>
+          <t>27,92%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>21,14%</t>
+          <t>17,2%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>40,95%</t>
+          <t>37,91%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2510,32 +2510,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>28845</t>
+          <t>26593</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>21263</t>
+          <t>20297</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>35941</t>
+          <t>33238</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>29,41%</t>
+          <t>29,07%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>21,68%</t>
+          <t>22,18%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>36,65%</t>
+          <t>36,33%</t>
         </is>
       </c>
     </row>
@@ -2548,72 +2548,72 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>32980</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>28252</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>37396</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>69,86%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>59,84%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>79,21%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>54</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>31891</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>26466</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>36036</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>72,01%</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>59,76%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>81,36%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>37336</t>
+          <t>31922</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>31760</t>
+          <t>27498</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>42413</t>
+          <t>36670</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>69,42%</t>
+          <t>72,08%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>59,05%</t>
+          <t>62,09%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>78,86%</t>
+          <t>82,8%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2623,32 +2623,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>69227</t>
+          <t>64902</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>62131</t>
+          <t>58257</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>76809</t>
+          <t>71198</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>70,59%</t>
+          <t>70,93%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>63,35%</t>
+          <t>63,67%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>78,32%</t>
+          <t>77,82%</t>
         </is>
       </c>
     </row>
@@ -2661,57 +2661,57 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>87</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>47209</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>47209</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>47209</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>74</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>44290</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>44290</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>44290</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>87</t>
-        </is>
-      </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>53782</t>
+          <t>44286</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>53782</t>
+          <t>44286</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>53782</t>
+          <t>44286</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2736,17 +2736,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>98072</t>
+          <t>91495</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>98072</t>
+          <t>91495</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>98072</t>
+          <t>91495</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2778,72 +2778,72 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>130</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>105247</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>96438</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>113829</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>74,87%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>68,6%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>80,98%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
           <t>136</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>94247</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>83774</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>102772</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>76,19%</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>67,73%</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>83,08%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>130</t>
-        </is>
-      </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>113929</t>
+          <t>93182</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>97399</t>
+          <t>83183</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>124911</t>
+          <t>100329</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>73,48%</t>
+          <t>76,49%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>62,82%</t>
+          <t>68,28%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>80,57%</t>
+          <t>82,36%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2853,32 +2853,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>208175</t>
+          <t>198430</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>190623</t>
+          <t>186556</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>222127</t>
+          <t>210484</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>74,68%</t>
+          <t>75,62%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>68,39%</t>
+          <t>71,1%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>79,69%</t>
+          <t>80,22%</t>
         </is>
       </c>
     </row>
@@ -2891,72 +2891,72 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>35324</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>26742</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>44133</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>25,13%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>19,02%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>31,4%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>38</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>29449</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>20924</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>39922</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>23,81%</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>16,92%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>32,27%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>46</t>
-        </is>
-      </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>41115</t>
+          <t>28640</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>30133</t>
+          <t>21493</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>57645</t>
+          <t>38639</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>26,52%</t>
+          <t>23,51%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>19,43%</t>
+          <t>17,64%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>37,18%</t>
+          <t>31,72%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2966,32 +2966,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>70565</t>
+          <t>63964</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>56613</t>
+          <t>51910</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>88117</t>
+          <t>75838</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>25,32%</t>
+          <t>24,38%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>20,31%</t>
+          <t>19,78%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>31,61%</t>
+          <t>28,9%</t>
         </is>
       </c>
     </row>
@@ -3004,57 +3004,57 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>176</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>140571</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>140571</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>140571</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
           <t>174</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>123696</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>123696</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>123696</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>176</t>
-        </is>
-      </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>155044</t>
+          <t>121822</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>155044</t>
+          <t>121822</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>155044</t>
+          <t>121822</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3079,17 +3079,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>278740</t>
+          <t>262394</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>278740</t>
+          <t>262394</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>278740</t>
+          <t>262394</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3121,72 +3121,72 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
+          <t>111</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>88822</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>76767</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>99618</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>56,53%</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>48,85%</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>63,4%</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
           <t>96</t>
         </is>
       </c>
-      <c r="D25" s="2" t="inlineStr">
-        <is>
-          <t>69315</t>
-        </is>
-      </c>
-      <c r="E25" s="2" t="inlineStr">
-        <is>
-          <t>60226</t>
-        </is>
-      </c>
-      <c r="F25" s="2" t="inlineStr">
-        <is>
-          <t>78553</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="inlineStr">
-        <is>
-          <t>53,87%</t>
-        </is>
-      </c>
-      <c r="H25" s="2" t="inlineStr">
-        <is>
-          <t>46,81%</t>
-        </is>
-      </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t>61,05%</t>
-        </is>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>111</t>
-        </is>
-      </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>86782</t>
+          <t>74308</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>74738</t>
+          <t>63826</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>97636</t>
+          <t>84358</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>56,29%</t>
+          <t>53,89%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>48,48%</t>
+          <t>46,28%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>63,33%</t>
+          <t>61,17%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3196,32 +3196,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>156097</t>
+          <t>163130</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>141991</t>
+          <t>148465</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>170399</t>
+          <t>180859</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>55,19%</t>
+          <t>55,29%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>50,21%</t>
+          <t>50,32%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>60,25%</t>
+          <t>61,3%</t>
         </is>
       </c>
     </row>
@@ -3234,72 +3234,72 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
+          <t>91</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>68314</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>57518</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>80369</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>43,47%</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>36,6%</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>51,15%</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
           <t>88</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
-        <is>
-          <t>59350</t>
-        </is>
-      </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>50112</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>68439</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>46,13%</t>
-        </is>
-      </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>38,95%</t>
-        </is>
-      </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>53,19%</t>
-        </is>
-      </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>91</t>
-        </is>
-      </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>67377</t>
+          <t>63592</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>56523</t>
+          <t>53542</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>79421</t>
+          <t>74074</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>43,71%</t>
+          <t>46,11%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>36,67%</t>
+          <t>38,83%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>51,52%</t>
+          <t>53,72%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3309,32 +3309,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>126726</t>
+          <t>131906</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>112424</t>
+          <t>114177</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>140832</t>
+          <t>146571</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>44,81%</t>
+          <t>44,71%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>39,75%</t>
+          <t>38,7%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>49,79%</t>
+          <t>49,68%</t>
         </is>
       </c>
     </row>
@@ -3347,57 +3347,57 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
+          <t>202</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>157136</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>157136</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>157136</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
           <t>184</t>
         </is>
       </c>
-      <c r="D27" s="2" t="inlineStr">
-        <is>
-          <t>128665</t>
-        </is>
-      </c>
-      <c r="E27" s="2" t="inlineStr">
-        <is>
-          <t>128665</t>
-        </is>
-      </c>
-      <c r="F27" s="2" t="inlineStr">
-        <is>
-          <t>128665</t>
-        </is>
-      </c>
-      <c r="G27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J27" s="2" t="inlineStr">
-        <is>
-          <t>202</t>
-        </is>
-      </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>154159</t>
+          <t>137900</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>154159</t>
+          <t>137900</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>154159</t>
+          <t>137900</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3422,17 +3422,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>282823</t>
+          <t>295036</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>282823</t>
+          <t>295036</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>282823</t>
+          <t>295036</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3464,72 +3464,72 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>505</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>380108</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>356711</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>407480</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>55,34%</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>51,94%</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>59,33%</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
           <t>535</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
-        <is>
-          <t>361860</t>
-        </is>
-      </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>311478</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>388284</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>55,4%</t>
-        </is>
-      </c>
-      <c r="H28" s="2" t="inlineStr">
-        <is>
-          <t>47,69%</t>
-        </is>
-      </c>
-      <c r="I28" s="2" t="inlineStr">
-        <is>
-          <t>59,45%</t>
-        </is>
-      </c>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t>505</t>
-        </is>
-      </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>405593</t>
+          <t>360446</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>378260</t>
+          <t>337793</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>431631</t>
+          <t>380812</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>54,46%</t>
+          <t>58,31%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>50,79%</t>
+          <t>54,64%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>57,96%</t>
+          <t>61,6%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3539,32 +3539,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>767453</t>
+          <t>740553</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>715739</t>
+          <t>707394</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>806798</t>
+          <t>776670</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>54,9%</t>
+          <t>56,75%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>51,2%</t>
+          <t>54,21%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>57,72%</t>
+          <t>59,51%</t>
         </is>
       </c>
     </row>
@@ -3577,72 +3577,72 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
+          <t>435</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>306716</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>279344</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>330113</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>44,66%</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>40,67%</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>48,06%</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
           <t>380</t>
         </is>
       </c>
-      <c r="D29" s="2" t="inlineStr">
-        <is>
-          <t>291274</t>
-        </is>
-      </c>
-      <c r="E29" s="2" t="inlineStr">
-        <is>
-          <t>264850</t>
-        </is>
-      </c>
-      <c r="F29" s="2" t="inlineStr">
-        <is>
-          <t>341656</t>
-        </is>
-      </c>
-      <c r="G29" s="2" t="inlineStr">
-        <is>
-          <t>44,6%</t>
-        </is>
-      </c>
-      <c r="H29" s="2" t="inlineStr">
-        <is>
-          <t>40,55%</t>
-        </is>
-      </c>
-      <c r="I29" s="2" t="inlineStr">
-        <is>
-          <t>52,31%</t>
-        </is>
-      </c>
-      <c r="J29" s="2" t="inlineStr">
-        <is>
-          <t>435</t>
-        </is>
-      </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>339140</t>
+          <t>257762</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>313102</t>
+          <t>237396</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>366473</t>
+          <t>280415</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>45,54%</t>
+          <t>41,69%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>42,04%</t>
+          <t>38,4%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>49,21%</t>
+          <t>45,36%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3652,32 +3652,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>630414</t>
+          <t>564478</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>591069</t>
+          <t>528361</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>682128</t>
+          <t>597637</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>45,1%</t>
+          <t>43,25%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>42,28%</t>
+          <t>40,49%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>48,8%</t>
+          <t>45,79%</t>
         </is>
       </c>
     </row>
@@ -3690,57 +3690,57 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
+          <t>940</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>686824</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>686824</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>686824</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
           <t>915</t>
         </is>
       </c>
-      <c r="D30" s="2" t="inlineStr">
-        <is>
-          <t>653134</t>
-        </is>
-      </c>
-      <c r="E30" s="2" t="inlineStr">
-        <is>
-          <t>653134</t>
-        </is>
-      </c>
-      <c r="F30" s="2" t="inlineStr">
-        <is>
-          <t>653134</t>
-        </is>
-      </c>
-      <c r="G30" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H30" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I30" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J30" s="2" t="inlineStr">
-        <is>
-          <t>940</t>
-        </is>
-      </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>744733</t>
+          <t>618208</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>744733</t>
+          <t>618208</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>744733</t>
+          <t>618208</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3765,17 +3765,17 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>1397867</t>
+          <t>1305031</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>1397867</t>
+          <t>1305031</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>1397867</t>
+          <t>1305031</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
